--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:20</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -722,31 +722,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1초에 100만원</t>
+          <t>야생에서 갤러리를 얻었다</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=842977&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855027&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>842977</t>
+          <t>855027</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:21</t>
+          <t>2026-09-21 12:50:05</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>이지호</t>
+          <t>달아</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -814,31 +814,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>물고 뜯고 속이고</t>
+          <t>박수진과 백서정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854643&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854592&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>854643</t>
+          <t>854592</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:22</t>
+          <t>2026-09-21 12:50:05</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>나음</t>
+          <t>옹방</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -906,35 +906,39 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>딜리버리 임파서블</t>
+          <t>하트는 파랑</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854757&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=852620&amp;tab=tue</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>854757</t>
+          <t>852620</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>2026-09-21 12:50:08</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5보2</t>
+        </is>
+      </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>not_found</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -994,31 +998,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>혈마전기</t>
+          <t>천씨세가의 망나니가 되었다</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854518&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=847541&amp;tab=tue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>854518</t>
+          <t>847541</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:25</t>
+          <t>2026-09-21 12:50:08</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>자몽소년</t>
+          <t>오수휘</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1086,31 +1090,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보이드맨</t>
+          <t>내 남편의 정부에게</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=827173&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=817366&amp;tab=tue</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>827173</t>
+          <t>817366</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:26</t>
+          <t>2026-09-21 12:50:08</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>한건희</t>
+          <t>에리카</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1169,40 +1173,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>조의 영역: 여의도</t>
+          <t>선 넘는 결혼생활</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854589&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=834750&amp;tab=tue</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>854589</t>
+          <t>834750</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:26</t>
+          <t>2026-09-21 12:50:09</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>조석</t>
+          <t>맹</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1220,12 +1224,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1270,7 +1274,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1289,7 +1293,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:28</t>
+          <t>2026-09-21 12:50:11</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1382,31 +1386,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>상속자들 사이에서 살아남기</t>
+          <t>고하이런</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854560&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853092&amp;tab=wed</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>854560</t>
+          <t>853092</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:29</t>
+          <t>2026-09-21 12:50:11</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>소어링</t>
+          <t>지민수</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1474,31 +1478,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>빌드업</t>
+          <t>착각 연애</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=750826&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854786&amp;tab=wed</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>750826</t>
+          <t>854786</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:30</t>
+          <t>2026-09-21 12:50:12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1566,7 +1570,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1585,7 +1589,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:32</t>
+          <t>2026-09-21 12:50:14</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1678,31 +1682,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>그림으로 승부</t>
+          <t>세계멸망전</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853095&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854580&amp;tab=thu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>853095</t>
+          <t>854580</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:33</t>
+          <t>2026-09-21 12:50:15</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>웡웡이</t>
+          <t>펀치킥</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1770,31 +1774,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>사랑받고 자란</t>
+          <t>헤어지기 싫어!</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854549&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854825&amp;tab=thu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>854549</t>
+          <t>854825</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:33</t>
+          <t>2026-09-21 12:50:15</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>주키</t>
+          <t>해례</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1853,40 +1857,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>새동네</t>
+          <t>이세계 캠핑으로 힐링 라이프</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=817752&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=823971&amp;tab=thu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>817752</t>
+          <t>823971</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:36</t>
+          <t>2026-09-21 12:50:15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>림스</t>
+          <t>일인분</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1904,12 +1908,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1954,31 +1958,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>첫정</t>
+          <t>이세계 만물슈퍼</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=844061&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854823&amp;tab=fri</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>844061</t>
+          <t>854823</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:36</t>
+          <t>2026-09-21 12:50:18</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>혜윤</t>
+          <t>손병준</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -2046,31 +2050,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>남편을 죽이고 저택을 상속받았다</t>
+          <t>내가 쓴 공포 소설에서 살아남는 법</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854857&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854260&amp;tab=fri</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>854857</t>
+          <t>854260</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:36</t>
+          <t>2026-09-21 12:50:18</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LICO</t>
+          <t>불보라</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2138,31 +2142,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>단둘이는 안 돼!</t>
+          <t>회귀수선전</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=838944&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=839827&amp;tab=fri</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>838944</t>
+          <t>839827</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:37</t>
+          <t>2026-09-21 12:50:18</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>멜로로</t>
+          <t>김무현</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2221,40 +2225,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>새끼부터 시작하는 악마생활</t>
+          <t>도무지 그애는</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854302&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=761496&amp;tab=fri</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>854302</t>
+          <t>761496</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:39</t>
+          <t>2026-09-21 12:50:19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>화현</t>
+          <t>게코</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2272,12 +2276,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2326,27 +2330,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>같은 학교 친구</t>
+          <t>싸움이 너무 쉽다</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=774832&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855035&amp;tab=sat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>774832</t>
+          <t>855035</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:40</t>
+          <t>2026-09-21 12:50:22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>유유</t>
+          <t>정상</t>
         </is>
       </c>
       <c r="I20" t="b">
@@ -2405,40 +2409,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>태은민호만화</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854519&amp;tab=sat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>854519</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:43</t>
+          <t>2026-09-21 12:50:22</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>가량</t>
         </is>
       </c>
       <c r="I21" t="b">
@@ -2451,17 +2455,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2475,36 +2479,16 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -2517,40 +2501,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>스페이스 마린에게 상태창이 생김</t>
+          <t>유령의 노래</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854613&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=823239&amp;tab=sat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>854613</t>
+          <t>823239</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:43</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>꿀범</t>
+          <t>김문경</t>
         </is>
       </c>
       <c r="I22" t="b">
@@ -2568,12 +2552,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2609,40 +2593,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>무조건 이혼한다</t>
+          <t>호붕빵 아저씨</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=842623&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=833361&amp;tab=sat</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>842623</t>
+          <t>833361</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>모닥불</t>
+          <t>정다운</t>
         </is>
       </c>
       <c r="I23" t="b">
@@ -2660,12 +2644,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2710,31 +2694,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>태엽 위를 걷는 연인</t>
+          <t>2026 루키 단편선</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854367&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>854367</t>
+          <t>853869</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:24</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>아르누니</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I24" t="b">
@@ -2747,17 +2731,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>월, 수, 목, 일 연재</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2771,16 +2755,36 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI24" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -2802,31 +2806,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>당신의 라이언</t>
+          <t>용사의 발라드</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841490&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854122&amp;tab=sun</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>841490</t>
+          <t>854122</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:25</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>몽찌</t>
+          <t>남웅</t>
         </is>
       </c>
       <c r="I25" t="b">
@@ -2894,7 +2898,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2913,7 +2917,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:25</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:03</t>
+          <t>2026-09-28 13:12:27</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,40 +713,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>야생에서 갤러리를 얻었다</t>
+          <t>레디액션</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855027&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855128&amp;tab=tue</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>855027</t>
+          <t>855128</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:05</t>
+          <t>2026-09-28 13:12:31</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>달아</t>
+          <t>나근H</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -764,12 +764,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -805,40 +805,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>박수진과 백서정</t>
+          <t>2026 루키 단편선</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854592&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=wed</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>854592</t>
+          <t>853869</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:05</t>
+          <t>2026-09-28 13:12:32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>옹방</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -851,17 +851,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>월, 수, 목, 일 연재</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -875,16 +875,36 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Y4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -897,40 +917,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>하트는 파랑</t>
+          <t>폐쇄교실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=852620&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855285&amp;tab=wed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>852620</t>
+          <t>855285</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:08</t>
+          <t>2026-09-28 13:12:33</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5보2</t>
+          <t>김갈마</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -948,12 +968,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -989,40 +1009,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>천씨세가의 망나니가 되었다</t>
+          <t>사자의 코털을 건드린 것 같아요</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=847541&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854832&amp;tab=wed</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>847541</t>
+          <t>854832</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:08</t>
+          <t>2026-09-28 13:12:34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>오수휘</t>
+          <t>이깜누</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1040,12 +1060,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1081,40 +1101,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>내 남편의 정부에게</t>
+          <t>2026 루키 단편선</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=817366&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=thu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>817366</t>
+          <t>853869</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:08</t>
+          <t>2026-09-28 13:12:36</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>에리카</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1127,17 +1147,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>월, 수, 목, 일 연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1151,16 +1171,36 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1173,40 +1213,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>선 넘는 결혼생활</t>
+          <t>신들의 단톡방에 김치사발면을 바쳤다</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=834750&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855151&amp;tab=thu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>834750</t>
+          <t>855151</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:09</t>
+          <t>2026-09-28 13:12:36</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>맹</t>
+          <t>LICO</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1224,12 +1264,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1265,63 +1305,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>89</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>장난질</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854375&amp;tab=thu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>854375</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:11</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>네이버웹툰</t>
-        </is>
-      </c>
+          <t>2026-09-28 13:12:37</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>월, 수, 목, 일 연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1335,36 +1367,16 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1377,40 +1389,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>고하이런</t>
+          <t>공주는 용의 뱃속에</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853092&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853535&amp;tab=fri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>853092</t>
+          <t>853535</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:11</t>
+          <t>2026-09-28 13:12:40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>지민수</t>
+          <t>마요너구리</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1428,12 +1440,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1469,40 +1481,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>착각 연애</t>
+          <t>에러 디 에코</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854786&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854335&amp;tab=fri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>854786</t>
+          <t>854335</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:12</t>
+          <t>2026-09-28 13:12:40</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>순수</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1520,12 +1532,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1561,40 +1573,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>꿇어보세요, 대공님!</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=836707&amp;tab=fri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>836707</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:14</t>
+          <t>2026-09-28 13:12:42</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>가천가</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1607,17 +1619,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1631,36 +1643,16 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1673,40 +1665,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>세계멸망전</t>
+          <t>용사는 쉴 수 없다</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854580&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855296&amp;tab=sat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>854580</t>
+          <t>855296</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:15</t>
+          <t>2026-09-28 13:12:44</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>펀치킥</t>
+          <t>판테라</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1724,12 +1716,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1765,40 +1757,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>헤어지기 싫어!</t>
+          <t>대디, 대디</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854825&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855057&amp;tab=sat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>854825</t>
+          <t>855057</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:15</t>
+          <t>2026-09-28 13:12:45</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>해례</t>
+          <t>정언</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1816,12 +1808,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1857,40 +1849,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>이세계 캠핑으로 힐링 라이프</t>
+          <t>2026 루키 단편선</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=823971&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>823971</t>
+          <t>853869</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:15</t>
+          <t>2026-09-28 13:12:47</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>일인분</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1903,17 +1895,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>월, 수, 목, 일 연재</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1927,16 +1919,36 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
+      <c r="Y15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1949,40 +1961,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>이세계 만물슈퍼</t>
+          <t>내 조선에 세종은 없다</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854823&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854524&amp;tab=sun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>854823</t>
+          <t>854524</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:18</t>
+          <t>2026-09-28 13:12:48</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>손병준</t>
+          <t>이재헌</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -2000,12 +2012,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2041,40 +2053,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>내가 쓴 공포 소설에서 살아남는 법</t>
+          <t>공작의 첫날밤을 빼앗은 쓰레기 영애</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854260&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855069&amp;tab=sun</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>854260</t>
+          <t>855069</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:18</t>
+          <t>2026-09-28 13:12:49</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>불보라</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2092,12 +2104,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2133,40 +2145,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>회귀수선전</t>
+          <t>Mickey x F1 정상을 향한 질주</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=839827&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>839827</t>
+          <t>849113</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-21 12:50:18</t>
+          <t>2026-09-28 13:12:49</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>김무현</t>
+          <t>Brandon Chen</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2184,12 +2196,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2203,798 +2215,42 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
       <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI18" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
       <c r="AJ18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>98</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>도무지 그애는</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=761496&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>761496</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:19</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>게코</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>88</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>싸움이 너무 쉽다</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855035&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>855035</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:22</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>99</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>태은민호만화</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854519&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>854519</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:22</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>가량</t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>127</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>유령의 노래</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=823239&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>823239</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:23</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>김문경</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>128</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>호붕빵 아저씨</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=833361&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>833361</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:23</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>정다운</t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>51</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026 루키 단편선</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>853869</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:24</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>네이버웹툰</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>월, 수, 목, 일 연재</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>mon,wed,thu,sun</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>mon,wed,thu,sun</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>78</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>용사의 발라드</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854122&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>854122</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:25</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>남웅</t>
-        </is>
-      </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>106</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>849113</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-09-21 12:50:25</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Brandon Chen</t>
-        </is>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ26" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,31 +610,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>무신급 막내가 되었다</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855342&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>855342</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:27</t>
+          <t>2026-10-05 13:35:33</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>레블스튜디오</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -647,17 +647,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -671,36 +671,16 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -713,40 +693,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>레디액션</t>
+          <t>2026 루키 단편선</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855128&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>855128</t>
+          <t>853869</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:31</t>
+          <t>2026-10-05 13:35:33</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>나근H</t>
+          <t>네이버웹툰</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -759,17 +739,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>월, 수, 목, 일 연재</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon,wed,thu,sun</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -783,16 +763,36 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Y3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -805,40 +805,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>함부로 친절하지 말라</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=821095&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>821095</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:32</t>
+          <t>2026-10-05 13:35:34</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>아린</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -851,17 +851,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -875,36 +875,16 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -917,40 +897,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>폐쇄교실</t>
+          <t>박수진과 백서정</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855285&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854592&amp;tab=mon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>855285</t>
+          <t>854592</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:33</t>
+          <t>2026-10-05 13:35:34</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>김갈마</t>
+          <t>옹방</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -968,12 +948,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1009,40 +989,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사자의 코털을 건드린 것 같아요</t>
+          <t>남4친</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854832&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=841069&amp;tab=mon</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>854832</t>
+          <t>841069</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:34</t>
+          <t>2026-10-05 13:35:34</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>이깜누</t>
+          <t>올챙구리</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1060,12 +1040,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1101,40 +1081,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>기생번식</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845885&amp;tab=mon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>845885</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:36</t>
+          <t>2026-10-05 13:35:34</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>바쉬</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1147,17 +1127,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1171,36 +1151,16 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1213,40 +1173,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>신들의 단톡방에 김치사발면을 바쳤다</t>
+          <t>제국 최고의 악녀를 사랑하게 되었습니다</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855151&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=833908&amp;tab=mon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>855151</t>
+          <t>833908</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:36</t>
+          <t>2026-10-05 13:35:34</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LICO</t>
+          <t>아지</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1264,12 +1224,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1305,55 +1265,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>장난질</t>
+          <t>머저리 M수생</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854375&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=845214&amp;tab=mon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>854375</t>
+          <t>845214</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:37</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>2026-10-05 13:35:34</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>규정</t>
+        </is>
+      </c>
       <c r="I9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1389,40 +1357,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>공주는 용의 뱃속에</t>
+          <t>모솔대첩</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853535&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=833596&amp;tab=mon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>853535</t>
+          <t>833596</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:40</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>마요너구리</t>
+          <t>진자</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1440,12 +1408,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1481,40 +1449,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>에러 디 에코</t>
+          <t>양심과외</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854335&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=847903&amp;tab=mon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>854335</t>
+          <t>847903</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:40</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>순수</t>
+          <t>리나</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1532,12 +1500,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1573,40 +1541,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>꿇어보세요, 대공님!</t>
+          <t>꽃과 재</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=836707&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=848711&amp;tab=mon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>836707</t>
+          <t>848711</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:42</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>가천가</t>
+          <t>우루</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1624,12 +1592,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1665,40 +1633,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>용사는 쉴 수 없다</t>
+          <t>Lv.99 흑염의 프린세스</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855296&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=838075&amp;tab=mon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>855296</t>
+          <t>838075</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:44</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>판테라</t>
+          <t>YDR</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1716,12 +1684,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1757,40 +1725,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>대디, 대디</t>
+          <t>마왕의 빛나는 별</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855057&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843072&amp;tab=mon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>855057</t>
+          <t>843072</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:45</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>정언</t>
+          <t>이잉간</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1808,12 +1776,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1849,40 +1817,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>NPC를 죽였다</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846079&amp;tab=mon</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>846079</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:47</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>무공</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1895,17 +1863,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1919,36 +1887,16 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1961,40 +1909,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>내 조선에 세종은 없다</t>
+          <t>언스탯</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854524&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=846057&amp;tab=mon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>854524</t>
+          <t>846057</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:48</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>이재헌</t>
+          <t>쏜</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -2012,12 +1960,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2053,40 +2001,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>공작의 첫날밤을 빼앗은 쓰레기 영애</t>
+          <t>어떻게 용사 이름이 아아아아</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855069&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=842370&amp;tab=mon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>855069</t>
+          <t>842370</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:49</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>알그</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -2104,12 +2052,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2145,40 +2093,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>사랑해줄까?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854423&amp;tab=mon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>854423</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-28 13:12:49</t>
+          <t>2026-10-05 13:35:35</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>히히</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -2196,12 +2144,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2215,42 +2163,4946 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr">
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>89</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>누가 죄인인가</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846782&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>846782</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>90</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>헤어져서 팝니다</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850709&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>850709</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>헛둘</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>91</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>기로의 밤</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853687&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>853687</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DOCI</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>92</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>채널명 : 구찬지아</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841486&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>841486</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>김기현</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>93</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>마귀공주</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852115&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>852115</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>햄스터빵디</t>
+        </is>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>94</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>나의 보이소프렌드</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=819698&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>819698</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>망공이</t>
+        </is>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>95</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>게임마스터</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=832104&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>832104</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>둥치</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>96</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>불완전한 이혼의 결말</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=838556&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>838556</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>진원</t>
+        </is>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>97</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>프로젝트 마르스</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=837999&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>837999</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>영주</t>
+        </is>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>98</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>코너트 성 집사로 살아남기</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=844064&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>844064</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>LICO</t>
+        </is>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>99</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>너의 완두콩을 먹고 싶어!</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839082&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>839082</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>니소라스</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>공주는 헬스장에 간다</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=852173&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>852173</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>콕</t>
+        </is>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>101</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>네 앞에서만 부끄러운 나는</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=845496&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>845496</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>김현아</t>
+        </is>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>102</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>28, 청춘!</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853838&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>853838</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>이나라</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>103</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>뻐꾸기는 운다</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=850661&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>850661</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>진요</t>
+        </is>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>104</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>한국에서 히어로 하기 힘들더라</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=829666&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>829666</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>이해력</t>
+        </is>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>105</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>아직 제목 없음</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=831547&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>831547</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>주영현</t>
+        </is>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>106</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>주희의 주위</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849058&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>849058</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>107</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>솔로스쿨</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=824208&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>824208</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>랑쓰</t>
+        </is>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>108</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>비터사이드 크렌베리스</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841755&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>841755</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>챠콜</t>
+        </is>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>109</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>달로 만든 아이</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=784107&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>784107</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>온윤</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>110</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>킬링가드</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853116&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>853116</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>이제환</t>
+        </is>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>111</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>부활성녀</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853115&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>853115</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:35</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>사리앵</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>112</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>반도대탈출</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851869&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>851869</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>카시모프</t>
+        </is>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>113</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>귀신이 곡할 노릇</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849480&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>849480</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>배아령</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>114</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>데빌 캐피탈</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=846866&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>846866</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>정민용</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>115</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>웅녀님이 보우하사</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842322&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>842322</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>영파카</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>116</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>철이 없어서 그래</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=847435&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>847435</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>심도수</t>
+        </is>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>117</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>슬로우 다이브</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=839087&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>839087</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>고다</t>
+        </is>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>좋아하면 닮는댔어</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=842184&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>842184</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>문주</t>
+        </is>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>119</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>유체를 이탈하였습니다</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=851839&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>851839</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>이슬</t>
+        </is>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>120</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>인생도 도네가 되나요</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855297&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>855297</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>깜돌</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>월</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>121</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>미친 도련님은 일상이 계략</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855298&amp;tab=mon</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>855298</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:36</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>배조</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>54</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>표현이 서툰 여자애</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855294&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>855294</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:37</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>게게겍</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>84</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>맞불결혼</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855152&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>855152</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:38</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LICO</t>
+        </is>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>33</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>드래곤 여친이 귀환했다</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855153&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>855153</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:40</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LICO</t>
+        </is>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>41</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026 루키 단편선</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>853869</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:40</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>월, 수, 목, 일 연재</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ18" t="b">
+      <c r="AJ55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>73</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>남자친구의 결혼식</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855391&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>855391</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:41</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>비티</t>
+        </is>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>수</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>112</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>S급 공무수행에 협조 부탁드립니다</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=843070&amp;tab=wed</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>843070</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:42</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>마귀</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>wed</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>43</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026 루키 단편선</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>853869</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:44</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>월, 수, 목, 일 연재</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>53</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>새벽인력</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853096&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>853096</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:44</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>김주현</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>70</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>공허의 절대적 미학</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855162&amp;tab=thu</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>855162</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:45</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>thu</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>43</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>발모광마</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855573&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>855573</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:47</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>이건</t>
+        </is>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>49</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>용도의 차이</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855632&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>855632</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:48</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>52</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>천중용문</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=835116&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>835116</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:48</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>군주</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>121</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>재입대만 7번째</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=837665&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>837665</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:50</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>이진수</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>43</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>작전명 순정</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=793275&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>793275</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:51</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>꼬까리</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>75</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>호감도로 스킬 복사!</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855599&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>855599</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>지대공마법소년</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>44</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026 루키 단편선</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>853869</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:55</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>네이버웹툰</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>월, 수, 목, 일 연재</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>mon,wed,thu,sun</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>63</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>적귀</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855665&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>855665</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:56</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>88</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>극야 : 애프터폴</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=792694&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>792694</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:57</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>운</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>103</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>다 해 주는 오빠</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=855385&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>855385</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:57</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>라뇽</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>110</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-10-05 13:35:57</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ71" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,31 +610,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>몬스터와 힐링하는 S급 헌터</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=840845&amp;tab=mon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>840845</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:40</t>
+          <t>2026-10-19 12:41:48</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>팀 더 지크</t>
         </is>
       </c>
       <c r="I2" t="b">
@@ -647,17 +647,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -671,36 +671,16 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -722,31 +702,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>악당 가족이 독립을 반대한다</t>
+          <t>신입 공무원은 빌런 잡고 퇴근합니다</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=817365&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856191&amp;tab=mon</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>817365</t>
+          <t>856191</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:41</t>
+          <t>2026-10-19 12:41:49</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>밋츄</t>
+          <t>성구</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -818,34 +798,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>우리들의 속사정</t>
+          <t>트리거</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855893&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=764480&amp;tab=mon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>855893</t>
+          <t>764480</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:41</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>2026-10-19 12:41:49</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>고경빈</t>
+        </is>
+      </c>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>mon</t>
@@ -889,40 +877,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>월</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>하울링</t>
+          <t>지팔지꼰 연애록</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854794&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856116&amp;tab=mon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>854794</t>
+          <t>856116</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:42</t>
+          <t>2026-10-19 12:41:49</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WANKE</t>
+          <t>읏차</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -940,12 +928,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>mon</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -990,31 +978,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>함부로 먹지 말 것</t>
+          <t>소환진이 좀 이상해 보이는 건 기분 탓이겠지</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854824&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854761&amp;tab=tue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>854824</t>
+          <t>854761</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:43</t>
+          <t>2026-10-19 12:41:51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>문나영</t>
+          <t>기럭지미인</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1073,40 +1061,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>대공님의 신부는 지옥의 전사</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=839404&amp;tab=tue</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>839404</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:45</t>
+          <t>2026-10-19 12:41:52</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>개바시</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1119,17 +1107,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1143,36 +1131,16 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1194,31 +1162,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>사이버펑크의 해결사가 사는 법</t>
+          <t>지극히 평범한</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855686&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855949&amp;tab=wed</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>855686</t>
+          <t>855949</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:45</t>
+          <t>2026-10-19 12:41:53</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>나무꾼</t>
+          <t>하모</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1286,31 +1254,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>행복부동산에 어서 오세요!</t>
+          <t>주식토피아</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855591&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856109&amp;tab=wed</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>855591</t>
+          <t>856109</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:45</t>
+          <t>2026-10-19 12:41:53</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>핑크아레나</t>
+          <t>은나무</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1323,17 +1291,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1369,40 +1337,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>수</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>미연</t>
+          <t>겨울이 지나가는 시간</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=837864&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854615&amp;tab=thu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>837864</t>
+          <t>854615</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:46</t>
+          <t>2026-10-19 12:41:56</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>서녜</t>
+          <t>하힘</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1420,12 +1388,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>wed</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1461,40 +1429,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026 루키 단편선</t>
+          <t>괴담 마켓</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855894&amp;tab=fri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>853869</t>
+          <t>855894</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:48</t>
+          <t>2026-10-19 12:41:59</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>네이버웹툰</t>
+          <t>고얌</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1507,17 +1475,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>월, 수, 목, 일 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>mon,wed,thu,sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1531,36 +1499,16 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
+      <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr">
         <is>
           <t>needs_series_search</t>
@@ -1573,40 +1521,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>마도서를 줍다 마법사가 되다</t>
+          <t>대기업 탈출일지</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855671&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855719&amp;tab=sat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>855671</t>
+          <t>855719</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:48</t>
+          <t>2026-10-19 12:42:01</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>섭이53</t>
+          <t>요다</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1624,12 +1572,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1665,40 +1613,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>반드시 로맨틱</t>
+          <t>주식토피아</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855642&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856109&amp;tab=sat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>855642</t>
+          <t>856109</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:49</t>
+          <t>2026-10-19 12:42:01</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>원펀치래빗</t>
+          <t>은나무</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1711,17 +1659,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>연재</t>
+          <t>수, 토 연재</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>wed,sat</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1757,55 +1705,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>순결을 그대에게</t>
+          <t>카오스이론</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=821589&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855666&amp;tab=sun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>821589</t>
+          <t>855666</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:49</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>2026-10-19 12:42:05</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>노커</t>
+        </is>
+      </c>
       <c r="I14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>thu</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1841,40 +1797,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>죽음이 우리를 갈라 놓을 때까지</t>
+          <t>지상낙원</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855688&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=837645&amp;tab=sun</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>855688</t>
+          <t>837645</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:51</t>
+          <t>2026-10-19 12:42:05</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>김수지</t>
+          <t>달꼬냑</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1892,12 +1848,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1933,40 +1889,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>일</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>나를 사랑한 여자들</t>
+          <t>Mickey x F1 정상을 향한 질주</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855718&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>855718</t>
+          <t>849113</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-12 13:49:51</t>
+          <t>2026-10-19 12:42:05</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>항</t>
+          <t>Brandon Chen</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1984,12 +1940,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2003,790 +1959,42 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Y16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
       <c r="AJ16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>120</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>달이 없는 나라</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=780063&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>780063</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:52</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>엥비</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>80</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>메이드</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854905&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>854905</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:54</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>login_or_adult_required</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>11</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>별이삼샵</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=737628&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>737628</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:56</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>혀노</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>49</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026 루키 단편선</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853869&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>853869</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:57</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>네이버웹툰</t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>월, 수, 목, 일 연재</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>mon,wed,thu,sun</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>mon,wed,thu,sun</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>70</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>천화서고 대공자</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=805193&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>805193</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:57</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>90</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>럼버잭</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=853684&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>853684</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:57</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>룡키</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>100</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>N년째 외사랑</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855628&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>855628</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:58</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>일</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>113</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>849113</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-10-12 13:49:58</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Brandon Chen</t>
-        </is>
-      </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>sun</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>needs_series_search</t>
-        </is>
-      </c>
-      <c r="AJ24" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/weekly_mapping_recheck_targets.xlsx
+++ b/data/weekly_mapping_recheck_targets.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,63 +601,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>몬스터와 힐링하는 S급 헌터</t>
+          <t>끓는 점</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=840845&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855633&amp;tab=tue</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>840845</t>
+          <t>855633</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:48</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>팀 더 지크</t>
-        </is>
-      </c>
+          <t>2026-10-26 12:41:46</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>연재</t>
-        </is>
-      </c>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -693,40 +685,40 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>신입 공무원은 빌런 잡고 퇴근합니다</t>
+          <t>포은 : 임고의 별</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=856191&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856243&amp;tab=tue</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>856191</t>
+          <t>856243</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:49</t>
+          <t>2026-10-26 12:41:46</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>성구</t>
+          <t>무번</t>
         </is>
       </c>
       <c r="I3" t="b">
@@ -744,12 +736,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -785,40 +777,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>트리거</t>
+          <t>몬스터의 인방스타</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=764480&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855923&amp;tab=tue</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>764480</t>
+          <t>855923</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:49</t>
+          <t>2026-10-26 12:41:46</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>고경빈</t>
+          <t>턍</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -836,12 +828,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -877,40 +869,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>월</t>
+          <t>화</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지팔지꼰 연애록</t>
+          <t>청춘 러브썸</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=856116&amp;tab=mon</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=828920&amp;tab=tue</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>856116</t>
+          <t>828920</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:49</t>
+          <t>2026-10-26 12:41:47</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>읏차</t>
+          <t>홍덕</t>
         </is>
       </c>
       <c r="I5" t="b">
@@ -928,12 +920,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>mon</t>
+          <t>tue</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -978,31 +970,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>소환진이 좀 이상해 보이는 건 기분 탓이겠지</t>
+          <t>렌탈히어로</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854761&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=808804&amp;tab=tue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>854761</t>
+          <t>808804</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:51</t>
+          <t>2026-10-26 12:41:47</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>기럭지미인</t>
+          <t>포르토</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -1061,40 +1053,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>화</t>
+          <t>수</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대공님의 신부는 지옥의 전사</t>
+          <t>S급 사원으로 오해받는 중입니다</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=839404&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856125&amp;tab=wed</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>839404</t>
+          <t>856125</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:52</t>
+          <t>2026-10-26 12:41:48</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>개바시</t>
+          <t>성혜</t>
         </is>
       </c>
       <c r="I7" t="b">
@@ -1112,12 +1104,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>tue</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1162,31 +1154,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지극히 평범한</t>
+          <t>이 남자는 수리가 필요합니다</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855949&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856241&amp;tab=wed</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>855949</t>
+          <t>856241</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:53</t>
+          <t>2026-10-26 12:41:49</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>하모</t>
+          <t>장채산</t>
         </is>
       </c>
       <c r="I8" t="b">
@@ -1254,31 +1246,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>주식토피아</t>
+          <t>완전무결한 공작님께</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=856109&amp;tab=wed</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=843888&amp;tab=wed</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>856109</t>
+          <t>843888</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:53</t>
+          <t>2026-10-26 12:41:49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>은나무</t>
+          <t>솔트</t>
         </is>
       </c>
       <c r="I9" t="b">
@@ -1291,17 +1283,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>wed</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1346,31 +1338,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>겨울이 지나가는 시간</t>
+          <t>토커</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=854615&amp;tab=thu</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=855950&amp;tab=thu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>854615</t>
+          <t>855950</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:56</t>
+          <t>2026-10-26 12:41:51</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>하힘</t>
+          <t>H8</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1429,40 +1421,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>금</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>괴담 마켓</t>
+          <t>살아남은 너를 찬미하며</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855894&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856184&amp;tab=thu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>855894</t>
+          <t>856184</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-19 12:41:59</t>
+          <t>2026-10-26 12:41:51</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>고얌</t>
+          <t>화음</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1480,12 +1472,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>fri</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1521,40 +1513,40 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>대기업 탈출일지</t>
+          <t>완벽한 예나</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855719&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=829276&amp;tab=thu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>855719</t>
+          <t>829276</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-19 12:42:01</t>
+          <t>2026-10-26 12:41:52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>요다</t>
+          <t>이겨울</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1572,12 +1564,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1613,40 +1605,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>토</t>
+          <t>목</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>주식토피아</t>
+          <t>귀신새가 지저귀면</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=856109&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=824001&amp;tab=thu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>856109</t>
+          <t>824001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-19 12:42:01</t>
+          <t>2026-10-26 12:41:52</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>은나무</t>
+          <t>홍타래</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1659,17 +1651,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>연재</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1705,40 +1697,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>금</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>카오스이론</t>
+          <t>거짓말은 대담하게</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=855666&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856192&amp;tab=fri</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>855666</t>
+          <t>856192</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-19 12:42:05</t>
+          <t>2026-10-26 12:41:54</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>노커</t>
+          <t>한집</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1756,12 +1748,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>fri</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1797,40 +1789,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>지상낙원</t>
+          <t>내가 키운 남주가 집착한다</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=837645&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=854610&amp;tab=sat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>837645</t>
+          <t>854610</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-19 12:42:05</t>
+          <t>2026-10-26 12:41:57</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>달꼬냑</t>
+          <t>문솔</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1848,12 +1840,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1889,40 +1881,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일</t>
+          <t>토</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mickey x F1 정상을 향한 질주</t>
+          <t>상향혼 컨설팅</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=856441&amp;tab=sat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>849113</t>
+          <t>856441</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-19 12:42:05</t>
+          <t>2026-10-26 12:41:57</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandon Chen</t>
+          <t>매미</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1940,12 +1932,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>sat</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1959,42 +1951,310 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>no_result</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr">
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>몰락민족의 천재 기사</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=856208&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>856208</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:41:59</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>차우민</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>107</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>그날의 순정을 편집하자면</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=856246&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>856246</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:42:00</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>login_or_adult_required</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>needs_series_search</t>
+        </is>
+      </c>
+      <c r="AJ18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>일</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>115</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mickey x F1 정상을 향한 질주</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=849113&amp;tab=sun</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>849113</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:42:00</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Brandon Chen</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>연재</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>no_result</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>no_result</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>needs_series_search</t>
         </is>
       </c>
-      <c r="AJ16" t="b">
+      <c r="AJ19" t="b">
         <v>1</v>
       </c>
     </row>
